--- a/artfynd/A 522-2026 artfynd.xlsx
+++ b/artfynd/A 522-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1201,10 +1201,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131253208</v>
+        <v>131253213</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,29 +1212,24 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1244,10 +1239,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481427</v>
+        <v>481415</v>
       </c>
       <c r="R6" t="n">
-        <v>7065814</v>
+        <v>7065749</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1284,7 +1279,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gammal gran med grov bark.</t>
+          <t>Flera fruktkroppar i en upplyft granlåga av en knäckt granstam.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1293,6 +1288,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1318,12 +1314,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1341,10 +1337,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131253213</v>
+        <v>131253208</v>
       </c>
       <c r="B7" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,24 +1348,29 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1379,10 +1380,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481415</v>
+        <v>481427</v>
       </c>
       <c r="R7" t="n">
-        <v>7065749</v>
+        <v>7065814</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1419,7 +1420,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en upplyft granlåga av en knäckt granstam.</t>
+          <t>Ringhack, äldre, på stambasen av en gammal gran med grov bark.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1428,7 +1429,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1613,10 +1613,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131253210</v>
+        <v>131253218</v>
       </c>
       <c r="B9" t="n">
-        <v>58043</v>
+        <v>79244</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,50 +1624,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bodflon NÖ vid Ockerån, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481564</v>
+        <v>481450</v>
       </c>
       <c r="R9" t="n">
-        <v>7065776</v>
+        <v>7065721</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1702,23 +1689,44 @@
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Minst 2 livliga individer av talltita i flerskiktad barrblandskog med murknande björkhögstubbar för talltitans bohål.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre granskog med inslag av tall och björk. Olikåldriga träd, stor stamdiameterspridning och frekvent förekomst av gamla granar med grov bark och nedåthängande grenar.</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1736,10 +1744,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131253218</v>
+        <v>131253210</v>
       </c>
       <c r="B10" t="n">
-        <v>79244</v>
+        <v>58043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1747,37 +1755,50 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bodflon NÖ vid Ockerån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481450</v>
+        <v>481564</v>
       </c>
       <c r="R10" t="n">
-        <v>7065721</v>
+        <v>7065776</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1812,44 +1833,23 @@
           <t>2026-02-21</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Minst 2 livliga individer av talltita i flerskiktad barrblandskog med murknande björkhögstubbar för talltitans bohål.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre granskog med inslag av tall och björk. Olikåldriga träd, stor stamdiameterspridning och frekvent förekomst av gamla granar med grov bark och nedåthängande grenar.</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2417,6 +2417,1096 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131264891</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ockerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>481424</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7065645</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131264629</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ockerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>481416</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7065722</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131264631</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ockerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>481317</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7065599</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131264632</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ockerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>481464</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7065904</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131264637</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91829</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ockerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>481413</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7065595</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131264634</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91829</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ockerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>481411</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7065645</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131264636</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91829</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ockerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>481404</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7065693</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131264633</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91829</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ockerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>481647</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7065629</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131264630</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ockerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>481418</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7065682</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131264628</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ockerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>481651</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7065625</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>131264627</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ockerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>481654</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7065637</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 522-2026 artfynd.xlsx
+++ b/artfynd/A 522-2026 artfynd.xlsx
@@ -1201,10 +1201,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131253213</v>
+        <v>131253208</v>
       </c>
       <c r="B6" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,24 +1212,29 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1239,10 +1244,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481415</v>
+        <v>481427</v>
       </c>
       <c r="R6" t="n">
-        <v>7065749</v>
+        <v>7065814</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1279,7 +1284,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en upplyft granlåga av en knäckt granstam.</t>
+          <t>Ringhack, äldre, på stambasen av en gammal gran med grov bark.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,7 +1293,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1314,12 +1318,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1337,10 +1341,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131253208</v>
+        <v>131253213</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,29 +1352,24 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1380,10 +1379,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481427</v>
+        <v>481415</v>
       </c>
       <c r="R7" t="n">
-        <v>7065814</v>
+        <v>7065749</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1420,7 +1419,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gammal gran med grov bark.</t>
+          <t>Flera fruktkroppar i en upplyft granlåga av en knäckt granstam.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1429,6 +1428,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 522-2026 artfynd.xlsx
+++ b/artfynd/A 522-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131253220</v>
       </c>
       <c r="B2" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>131253217</v>
       </c>
       <c r="B3" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>131253216</v>
       </c>
       <c r="B5" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1201,10 +1201,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131253208</v>
+        <v>131253213</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>91830</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,29 +1212,24 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1244,10 +1239,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481427</v>
+        <v>481415</v>
       </c>
       <c r="R6" t="n">
-        <v>7065814</v>
+        <v>7065749</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1284,7 +1279,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gammal gran med grov bark.</t>
+          <t>Flera fruktkroppar i en upplyft granlåga av en knäckt granstam.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1293,6 +1288,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1318,12 +1314,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1341,10 +1337,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131253213</v>
+        <v>131253208</v>
       </c>
       <c r="B7" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,24 +1348,29 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1379,10 +1380,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481415</v>
+        <v>481427</v>
       </c>
       <c r="R7" t="n">
-        <v>7065749</v>
+        <v>7065814</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1419,7 +1420,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en upplyft granlåga av en knäckt granstam.</t>
+          <t>Ringhack, äldre, på stambasen av en gammal gran med grov bark.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1428,7 +1429,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1480,7 +1480,7 @@
         <v>131253219</v>
       </c>
       <c r="B8" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>131253218</v>
       </c>
       <c r="B9" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>131253211</v>
       </c>
       <c r="B11" t="n">
-        <v>91805</v>
+        <v>91806</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>131253215</v>
       </c>
       <c r="B12" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>131253214</v>
       </c>
       <c r="B13" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>131264637</v>
       </c>
       <c r="B19" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>131264634</v>
       </c>
       <c r="B20" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>131264636</v>
       </c>
       <c r="B21" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>131264633</v>
       </c>
       <c r="B22" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 522-2026 artfynd.xlsx
+++ b/artfynd/A 522-2026 artfynd.xlsx
@@ -1201,10 +1201,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131253213</v>
+        <v>131253208</v>
       </c>
       <c r="B6" t="n">
-        <v>91830</v>
+        <v>57884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,24 +1212,29 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1239,10 +1244,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481415</v>
+        <v>481427</v>
       </c>
       <c r="R6" t="n">
-        <v>7065749</v>
+        <v>7065814</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1279,7 +1284,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en upplyft granlåga av en knäckt granstam.</t>
+          <t>Ringhack, äldre, på stambasen av en gammal gran med grov bark.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,7 +1293,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1314,12 +1318,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1337,10 +1341,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131253208</v>
+        <v>131253213</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>91833</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,29 +1352,24 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1380,10 +1379,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481427</v>
+        <v>481415</v>
       </c>
       <c r="R7" t="n">
-        <v>7065814</v>
+        <v>7065749</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1420,7 +1419,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gammal gran med grov bark.</t>
+          <t>Flera fruktkroppar i en upplyft granlåga av en knäckt granstam.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1429,6 +1428,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1613,10 +1613,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131253218</v>
+        <v>131253210</v>
       </c>
       <c r="B9" t="n">
-        <v>79245</v>
+        <v>58043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,37 +1624,50 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bodflon NÖ vid Ockerån, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481450</v>
+        <v>481564</v>
       </c>
       <c r="R9" t="n">
-        <v>7065721</v>
+        <v>7065776</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1689,44 +1702,23 @@
           <t>2026-02-21</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Minst 2 livliga individer av talltita i flerskiktad barrblandskog med murknande björkhögstubbar för talltitans bohål.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre granskog med inslag av tall och björk. Olikåldriga träd, stor stamdiameterspridning och frekvent förekomst av gamla granar med grov bark och nedåthängande grenar.</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1744,10 +1736,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131253210</v>
+        <v>131253218</v>
       </c>
       <c r="B10" t="n">
-        <v>58043</v>
+        <v>79245</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1755,50 +1747,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bodflon NÖ vid Ockerån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481564</v>
+        <v>481450</v>
       </c>
       <c r="R10" t="n">
-        <v>7065776</v>
+        <v>7065721</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1833,23 +1812,44 @@
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Minst 2 livliga individer av talltita i flerskiktad barrblandskog med murknande björkhögstubbar för talltitans bohål.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre granskog med inslag av tall och björk. Olikåldriga träd, stor stamdiameterspridning och frekvent förekomst av gamla granar med grov bark och nedåthängande grenar.</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1870,7 +1870,7 @@
         <v>131253211</v>
       </c>
       <c r="B11" t="n">
-        <v>91806</v>
+        <v>91809</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>131264637</v>
       </c>
       <c r="B19" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>131264634</v>
       </c>
       <c r="B20" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>131264636</v>
       </c>
       <c r="B21" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>131264633</v>
       </c>
       <c r="B22" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 522-2026 artfynd.xlsx
+++ b/artfynd/A 522-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131253220</v>
       </c>
       <c r="B2" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>131253217</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>131253216</v>
       </c>
       <c r="B5" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>131253213</v>
       </c>
       <c r="B7" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>131253219</v>
       </c>
       <c r="B8" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>131253218</v>
       </c>
       <c r="B10" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>131253211</v>
       </c>
       <c r="B11" t="n">
-        <v>91809</v>
+        <v>91810</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>131253215</v>
       </c>
       <c r="B12" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>131253214</v>
       </c>
       <c r="B13" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2831,10 +2831,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131264637</v>
+        <v>131264634</v>
       </c>
       <c r="B19" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481413</v>
+        <v>481411</v>
       </c>
       <c r="R19" t="n">
-        <v>7065595</v>
+        <v>7065645</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131264634</v>
+        <v>131264637</v>
       </c>
       <c r="B20" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481411</v>
+        <v>481413</v>
       </c>
       <c r="R20" t="n">
-        <v>7065645</v>
+        <v>7065595</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3020,7 +3020,7 @@
         <v>131264636</v>
       </c>
       <c r="B21" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>131264633</v>
       </c>
       <c r="B22" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 522-2026 artfynd.xlsx
+++ b/artfynd/A 522-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131253220</v>
       </c>
       <c r="B2" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>131253217</v>
       </c>
       <c r="B3" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>131253207</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>131253216</v>
       </c>
       <c r="B5" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1201,10 +1201,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131253208</v>
+        <v>131253213</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>91836</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,29 +1212,24 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1244,10 +1239,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481427</v>
+        <v>481415</v>
       </c>
       <c r="R6" t="n">
-        <v>7065814</v>
+        <v>7065749</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1284,7 +1279,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gammal gran med grov bark.</t>
+          <t>Flera fruktkroppar i en upplyft granlåga av en knäckt granstam.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1293,6 +1288,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1318,12 +1314,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1341,10 +1337,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131253213</v>
+        <v>131253208</v>
       </c>
       <c r="B7" t="n">
-        <v>91834</v>
+        <v>57886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,24 +1348,29 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1379,10 +1380,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481415</v>
+        <v>481427</v>
       </c>
       <c r="R7" t="n">
-        <v>7065749</v>
+        <v>7065814</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1419,7 +1420,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en upplyft granlåga av en knäckt granstam.</t>
+          <t>Ringhack, äldre, på stambasen av en gammal gran med grov bark.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1428,7 +1429,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1480,7 +1480,7 @@
         <v>131253219</v>
       </c>
       <c r="B8" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1613,10 +1613,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131253210</v>
+        <v>131253218</v>
       </c>
       <c r="B9" t="n">
-        <v>58043</v>
+        <v>79248</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,50 +1624,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bodflon NÖ vid Ockerån, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481564</v>
+        <v>481450</v>
       </c>
       <c r="R9" t="n">
-        <v>7065776</v>
+        <v>7065721</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1702,23 +1689,44 @@
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Minst 2 livliga individer av talltita i flerskiktad barrblandskog med murknande björkhögstubbar för talltitans bohål.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre granskog med inslag av tall och björk. Olikåldriga träd, stor stamdiameterspridning och frekvent förekomst av gamla granar med grov bark och nedåthängande grenar.</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1736,10 +1744,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131253218</v>
+        <v>131253210</v>
       </c>
       <c r="B10" t="n">
-        <v>79246</v>
+        <v>58045</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1747,37 +1755,50 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bodflon NÖ vid Ockerån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481450</v>
+        <v>481564</v>
       </c>
       <c r="R10" t="n">
-        <v>7065721</v>
+        <v>7065776</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1812,44 +1833,23 @@
           <t>2026-02-21</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Minst 2 livliga individer av talltita i flerskiktad barrblandskog med murknande björkhögstubbar för talltitans bohål.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre granskog med inslag av tall och björk. Olikåldriga träd, stor stamdiameterspridning och frekvent förekomst av gamla granar med grov bark och nedåthängande grenar.</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1870,7 +1870,7 @@
         <v>131253211</v>
       </c>
       <c r="B11" t="n">
-        <v>91810</v>
+        <v>91812</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>131253215</v>
       </c>
       <c r="B12" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>131253214</v>
       </c>
       <c r="B13" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>131253209</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>131264891</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>131264629</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>131264631</v>
       </c>
       <c r="B17" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>131264632</v>
       </c>
       <c r="B18" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2831,10 +2831,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131264634</v>
+        <v>131264637</v>
       </c>
       <c r="B19" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481411</v>
+        <v>481413</v>
       </c>
       <c r="R19" t="n">
-        <v>7065645</v>
+        <v>7065595</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131264637</v>
+        <v>131264634</v>
       </c>
       <c r="B20" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481413</v>
+        <v>481411</v>
       </c>
       <c r="R20" t="n">
-        <v>7065595</v>
+        <v>7065645</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3020,7 +3020,7 @@
         <v>131264636</v>
       </c>
       <c r="B21" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>131264633</v>
       </c>
       <c r="B22" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>131264630</v>
       </c>
       <c r="B23" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>131264628</v>
       </c>
       <c r="B24" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>131264627</v>
       </c>
       <c r="B25" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 522-2026 artfynd.xlsx
+++ b/artfynd/A 522-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131253220</v>
       </c>
       <c r="B2" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>131253217</v>
       </c>
       <c r="B3" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>131253207</v>
       </c>
       <c r="B4" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>131253216</v>
       </c>
       <c r="B5" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>131253213</v>
       </c>
       <c r="B6" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>131253208</v>
       </c>
       <c r="B7" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>131253219</v>
       </c>
       <c r="B8" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>131253218</v>
       </c>
       <c r="B9" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>131253210</v>
       </c>
       <c r="B10" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>131253211</v>
       </c>
       <c r="B11" t="n">
-        <v>91812</v>
+        <v>91813</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>131253215</v>
       </c>
       <c r="B12" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>131253214</v>
       </c>
       <c r="B13" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>131253209</v>
       </c>
       <c r="B14" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>131264891</v>
       </c>
       <c r="B15" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>131264629</v>
       </c>
       <c r="B16" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>131264631</v>
       </c>
       <c r="B17" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>131264632</v>
       </c>
       <c r="B18" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>131264637</v>
       </c>
       <c r="B19" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>131264634</v>
       </c>
       <c r="B20" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>131264636</v>
       </c>
       <c r="B21" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>131264633</v>
       </c>
       <c r="B22" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>131264630</v>
       </c>
       <c r="B23" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>131264628</v>
       </c>
       <c r="B24" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>131264627</v>
       </c>
       <c r="B25" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 522-2026 artfynd.xlsx
+++ b/artfynd/A 522-2026 artfynd.xlsx
@@ -1613,10 +1613,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131253218</v>
+        <v>131253210</v>
       </c>
       <c r="B9" t="n">
-        <v>79249</v>
+        <v>58046</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,37 +1624,50 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bodflon NÖ vid Ockerån, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481450</v>
+        <v>481564</v>
       </c>
       <c r="R9" t="n">
-        <v>7065721</v>
+        <v>7065776</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1689,44 +1702,23 @@
           <t>2026-02-21</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Minst 2 livliga individer av talltita i flerskiktad barrblandskog med murknande björkhögstubbar för talltitans bohål.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre granskog med inslag av tall och björk. Olikåldriga träd, stor stamdiameterspridning och frekvent förekomst av gamla granar med grov bark och nedåthängande grenar.</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1744,10 +1736,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131253210</v>
+        <v>131253218</v>
       </c>
       <c r="B10" t="n">
-        <v>58046</v>
+        <v>79249</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1755,50 +1747,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bodflon NÖ vid Ockerån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481564</v>
+        <v>481450</v>
       </c>
       <c r="R10" t="n">
-        <v>7065776</v>
+        <v>7065721</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1833,23 +1812,44 @@
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Minst 2 livliga individer av talltita i flerskiktad barrblandskog med murknande björkhögstubbar för talltitans bohål.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre granskog med inslag av tall och björk. Olikåldriga träd, stor stamdiameterspridning och frekvent förekomst av gamla granar med grov bark och nedåthängande grenar.</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 522-2026 artfynd.xlsx
+++ b/artfynd/A 522-2026 artfynd.xlsx
@@ -1201,10 +1201,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131253213</v>
+        <v>131253208</v>
       </c>
       <c r="B6" t="n">
-        <v>91837</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,24 +1212,29 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1239,10 +1244,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481415</v>
+        <v>481427</v>
       </c>
       <c r="R6" t="n">
-        <v>7065749</v>
+        <v>7065814</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1279,7 +1284,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en upplyft granlåga av en knäckt granstam.</t>
+          <t>Ringhack, äldre, på stambasen av en gammal gran med grov bark.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,7 +1293,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1314,12 +1318,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1337,10 +1341,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131253208</v>
+        <v>131253213</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>91837</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,29 +1352,24 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1380,10 +1379,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481427</v>
+        <v>481415</v>
       </c>
       <c r="R7" t="n">
-        <v>7065814</v>
+        <v>7065749</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1420,7 +1419,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gammal gran med grov bark.</t>
+          <t>Flera fruktkroppar i en upplyft granlåga av en knäckt granstam.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1429,6 +1428,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 522-2026 artfynd.xlsx
+++ b/artfynd/A 522-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131253220</v>
       </c>
       <c r="B2" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>131253217</v>
       </c>
       <c r="B3" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>131253207</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>131253216</v>
       </c>
       <c r="B5" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>131253208</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>131253213</v>
       </c>
       <c r="B7" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>131253219</v>
       </c>
       <c r="B8" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1613,10 +1613,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131253210</v>
+        <v>131253218</v>
       </c>
       <c r="B9" t="n">
-        <v>58046</v>
+        <v>79250</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,50 +1624,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bodflon NÖ vid Ockerån, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481564</v>
+        <v>481450</v>
       </c>
       <c r="R9" t="n">
-        <v>7065776</v>
+        <v>7065721</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1702,23 +1689,44 @@
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Minst 2 livliga individer av talltita i flerskiktad barrblandskog med murknande björkhögstubbar för talltitans bohål.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre granskog med inslag av tall och björk. Olikåldriga träd, stor stamdiameterspridning och frekvent förekomst av gamla granar med grov bark och nedåthängande grenar.</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1736,10 +1744,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131253218</v>
+        <v>131253210</v>
       </c>
       <c r="B10" t="n">
-        <v>79249</v>
+        <v>58047</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1747,37 +1755,50 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bodflon NÖ vid Ockerån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481450</v>
+        <v>481564</v>
       </c>
       <c r="R10" t="n">
-        <v>7065721</v>
+        <v>7065776</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1812,44 +1833,23 @@
           <t>2026-02-21</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Minst 2 livliga individer av talltita i flerskiktad barrblandskog med murknande björkhögstubbar för talltitans bohål.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre granskog med inslag av tall och björk. Olikåldriga träd, stor stamdiameterspridning och frekvent förekomst av gamla granar med grov bark och nedåthängande grenar.</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1870,7 +1870,7 @@
         <v>131253211</v>
       </c>
       <c r="B11" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>131253215</v>
       </c>
       <c r="B12" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>131253214</v>
       </c>
       <c r="B13" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>131253209</v>
       </c>
       <c r="B14" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>131264891</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>131264629</v>
       </c>
       <c r="B16" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>131264631</v>
       </c>
       <c r="B17" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>131264632</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>131264637</v>
       </c>
       <c r="B19" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>131264634</v>
       </c>
       <c r="B20" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>131264636</v>
       </c>
       <c r="B21" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>131264633</v>
       </c>
       <c r="B22" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>131264630</v>
       </c>
       <c r="B23" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>131264628</v>
       </c>
       <c r="B24" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>131264627</v>
       </c>
       <c r="B25" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 522-2026 artfynd.xlsx
+++ b/artfynd/A 522-2026 artfynd.xlsx
@@ -1201,10 +1201,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131253208</v>
+        <v>131253213</v>
       </c>
       <c r="B6" t="n">
-        <v>57888</v>
+        <v>91838</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,29 +1212,24 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1244,10 +1239,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481427</v>
+        <v>481415</v>
       </c>
       <c r="R6" t="n">
-        <v>7065814</v>
+        <v>7065749</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1284,7 +1279,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gammal gran med grov bark.</t>
+          <t>Flera fruktkroppar i en upplyft granlåga av en knäckt granstam.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1293,6 +1288,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1318,12 +1314,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1341,10 +1337,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131253213</v>
+        <v>131253208</v>
       </c>
       <c r="B7" t="n">
-        <v>91838</v>
+        <v>57888</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,24 +1348,29 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1379,10 +1380,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481415</v>
+        <v>481427</v>
       </c>
       <c r="R7" t="n">
-        <v>7065749</v>
+        <v>7065814</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1419,7 +1420,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en upplyft granlåga av en knäckt granstam.</t>
+          <t>Ringhack, äldre, på stambasen av en gammal gran med grov bark.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1428,7 +1429,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1613,10 +1613,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131253218</v>
+        <v>131253210</v>
       </c>
       <c r="B9" t="n">
-        <v>79250</v>
+        <v>58047</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,37 +1624,50 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bodflon NÖ vid Ockerån, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481450</v>
+        <v>481564</v>
       </c>
       <c r="R9" t="n">
-        <v>7065721</v>
+        <v>7065776</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1689,44 +1702,23 @@
           <t>2026-02-21</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Minst 2 livliga individer av talltita i flerskiktad barrblandskog med murknande björkhögstubbar för talltitans bohål.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre granskog med inslag av tall och björk. Olikåldriga träd, stor stamdiameterspridning och frekvent förekomst av gamla granar med grov bark och nedåthängande grenar.</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1744,10 +1736,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131253210</v>
+        <v>131253218</v>
       </c>
       <c r="B10" t="n">
-        <v>58047</v>
+        <v>79250</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1755,50 +1747,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bodflon NÖ vid Ockerån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481564</v>
+        <v>481450</v>
       </c>
       <c r="R10" t="n">
-        <v>7065776</v>
+        <v>7065721</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1833,23 +1812,44 @@
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Minst 2 livliga individer av talltita i flerskiktad barrblandskog med murknande björkhögstubbar för talltitans bohål.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre granskog med inslag av tall och björk. Olikåldriga träd, stor stamdiameterspridning och frekvent förekomst av gamla granar med grov bark och nedåthängande grenar.</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 522-2026 artfynd.xlsx
+++ b/artfynd/A 522-2026 artfynd.xlsx
@@ -1613,10 +1613,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131253210</v>
+        <v>131253218</v>
       </c>
       <c r="B9" t="n">
-        <v>58047</v>
+        <v>79250</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,50 +1624,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bodflon NÖ vid Ockerån, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481564</v>
+        <v>481450</v>
       </c>
       <c r="R9" t="n">
-        <v>7065776</v>
+        <v>7065721</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1702,23 +1689,44 @@
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Minst 2 livliga individer av talltita i flerskiktad barrblandskog med murknande björkhögstubbar för talltitans bohål.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre granskog med inslag av tall och björk. Olikåldriga träd, stor stamdiameterspridning och frekvent förekomst av gamla granar med grov bark och nedåthängande grenar.</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1736,10 +1744,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131253218</v>
+        <v>131253210</v>
       </c>
       <c r="B10" t="n">
-        <v>79250</v>
+        <v>58047</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1747,37 +1755,50 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bodflon NÖ vid Ockerån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481450</v>
+        <v>481564</v>
       </c>
       <c r="R10" t="n">
-        <v>7065721</v>
+        <v>7065776</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1812,44 +1833,23 @@
           <t>2026-02-21</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Minst 2 livliga individer av talltita i flerskiktad barrblandskog med murknande björkhögstubbar för talltitans bohål.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre granskog med inslag av tall och björk. Olikåldriga träd, stor stamdiameterspridning och frekvent förekomst av gamla granar med grov bark och nedåthängande grenar.</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
